--- a/080_Calibration/uTTA_Device_Calibration.xlsx
+++ b/080_Calibration/uTTA_Device_Calibration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\Eigenentwicklungen\GitHub\uTTA\080_Calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADF6D18-A92C-4422-A99B-6CD2B8309548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398C4E6C-EFF8-4676-92A2-AC6AB050825C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="804" xr2:uid="{5A948594-E980-4DDA-9D2E-A8D1945BB44F}"/>
+    <workbookView xWindow="690" yWindow="540" windowWidth="23010" windowHeight="12210" tabRatio="804" firstSheet="2" activeTab="11" xr2:uid="{5A948594-E980-4DDA-9D2E-A8D1945BB44F}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial Instructions" sheetId="38" r:id="rId1"/>
@@ -62,6 +62,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1213,7 +1216,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -1354,15 +1357,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7965,6 +7967,39 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>218.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>383.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>653.82500000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>902.35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1176.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1485.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1806.85</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2234.4749999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2706.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3129.8249999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3625.4</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -7972,8 +8007,41 @@
             <c:numRef>
               <c:f>ADC_I_CAL!$B$10:$B$33</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.000" A";0.000" A";;@</c:formatCode>
                 <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>0.78592236999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.39183725</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.3833506500000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.2963137499999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.3008923599999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4343944100000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.6115104699999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.17265117</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.9043339800000005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.454639999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13.268794</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -13184,30 +13252,30 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="F4" s="90" t="s">
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="F4" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="91"/>
+      <c r="B5" s="90"/>
       <c r="C5" s="37">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="F5" s="91" t="s">
+      <c r="F5" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="91"/>
+      <c r="G5" s="90"/>
       <c r="H5" s="37">
         <f>I9</f>
         <v>0</v>
@@ -16361,11 +16429,11 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="90" t="s">
+      <c r="D3" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -16386,9 +16454,9 @@
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="37" t="e">
+      <c r="E4" s="37">
         <f>SLOPE(Tabelle14[IMeasured],Tabelle14[ADC Count])</f>
-        <v>#DIV/0!</v>
+        <v>3.6635406305598355E-3</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>32</v>
@@ -16413,9 +16481,9 @@
       <c r="D5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="37" t="e">
+      <c r="E5" s="37">
         <f>INTERCEPT(Tabelle14[IMeasured],Tabelle14[ADC Count])</f>
-        <v>#DIV/0!</v>
+        <v>-1.1003703273766874E-2</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>33</v>
@@ -16434,17 +16502,17 @@
       <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="92"/>
+      <c r="B6" s="91"/>
       <c r="C6" s="2"/>
       <c r="D6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="34" t="e">
+      <c r="E6" s="34">
         <f>RSQ(Tabelle14[IMeasured],Tabelle14[ADC Count])</f>
-        <v>#DIV/0!</v>
+        <v>0.99999969481584627</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="2"/>
@@ -16461,8 +16529,8 @@
       <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="92"/>
-      <c r="B7" s="92"/>
+      <c r="A7" s="91"/>
+      <c r="B7" s="91"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -16481,8 +16549,8 @@
       <c r="R7" s="2"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="92"/>
-      <c r="B8" s="92"/>
+      <c r="A8" s="91"/>
+      <c r="B8" s="91"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -16527,8 +16595,12 @@
       <c r="R9" s="2"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="82"/>
-      <c r="B10" s="35"/>
+      <c r="A10" s="81">
+        <v>218.1</v>
+      </c>
+      <c r="B10" s="43">
+        <v>0.78592236999999998</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -16547,8 +16619,12 @@
       <c r="R10" s="2"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="82"/>
-      <c r="B11" s="35"/>
+      <c r="A11" s="81">
+        <v>383.75</v>
+      </c>
+      <c r="B11" s="43">
+        <v>1.39183725</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -16567,8 +16643,12 @@
       <c r="R11" s="2"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="82"/>
-      <c r="B12" s="35"/>
+      <c r="A12" s="81">
+        <v>653.82500000000005</v>
+      </c>
+      <c r="B12" s="43">
+        <v>2.3833506500000001</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -16587,8 +16667,12 @@
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="82"/>
-      <c r="B13" s="35"/>
+      <c r="A13" s="81">
+        <v>902.35</v>
+      </c>
+      <c r="B13" s="43">
+        <v>3.2963137499999999</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -16607,8 +16691,12 @@
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="82"/>
-      <c r="B14" s="35"/>
+      <c r="A14" s="81">
+        <v>1176.2</v>
+      </c>
+      <c r="B14" s="43">
+        <v>4.3008923599999997</v>
+      </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -16627,8 +16715,12 @@
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="82"/>
-      <c r="B15" s="35"/>
+      <c r="A15" s="81">
+        <v>1485.6</v>
+      </c>
+      <c r="B15" s="43">
+        <v>5.4343944100000003</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -16647,8 +16739,12 @@
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="82"/>
-      <c r="B16" s="35"/>
+      <c r="A16" s="81">
+        <v>1806.85</v>
+      </c>
+      <c r="B16" s="43">
+        <v>6.6115104699999998</v>
+      </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -16667,8 +16763,12 @@
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="82"/>
-      <c r="B17" s="35"/>
+      <c r="A17" s="81">
+        <v>2234.4749999999999</v>
+      </c>
+      <c r="B17" s="43">
+        <v>8.17265117</v>
+      </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -16687,8 +16787,12 @@
       <c r="R17" s="2"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="81"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="81">
+        <v>2706.25</v>
+      </c>
+      <c r="B18" s="43">
+        <v>9.9043339800000005</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -16707,8 +16811,12 @@
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="35">
+        <v>3129.8249999999998</v>
+      </c>
+      <c r="B19" s="43">
+        <v>11.454639999999999</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -16727,8 +16835,12 @@
       <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="35">
+        <v>3625.4</v>
+      </c>
+      <c r="B20" s="43">
+        <v>13.268794</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -17192,7 +17304,7 @@
     <mergeCell ref="D3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
@@ -17276,9 +17388,9 @@
       <c r="B3" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -17597,9 +17709,9 @@
       <c r="R14" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="S14" s="47" t="e">
+      <c r="S14" s="47">
         <f>I_ADC_Gain</f>
-        <v>#DIV/0!</v>
+        <v>3.6635406305598355E-3</v>
       </c>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
@@ -17626,9 +17738,9 @@
       <c r="R15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="S15" s="48" t="e">
+      <c r="S15" s="48">
         <f>I_ADC_Offs</f>
-        <v>#DIV/0!</v>
+        <v>-1.1003703273766874E-2</v>
       </c>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
@@ -19443,18 +19555,18 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -19466,14 +19578,14 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="84"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
+      <c r="A3" s="82"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -19485,18 +19597,18 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -19508,14 +19620,14 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="84"/>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
+      <c r="A5" s="82"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -19527,18 +19639,18 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="82" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -19550,14 +19662,14 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="84"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -19569,18 +19681,18 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="84" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -19592,14 +19704,14 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="84"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
+      <c r="A9" s="82"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -19611,18 +19723,18 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -19634,14 +19746,14 @@
       <c r="Q10" s="2"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="84"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -19653,18 +19765,18 @@
       <c r="Q11" s="2"/>
     </row>
     <row r="12" spans="1:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -19676,14 +19788,14 @@
       <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -19695,18 +19807,18 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="84" t="s">
+      <c r="A14" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="85" t="s">
+      <c r="B14" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="85"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -19718,14 +19830,14 @@
       <c r="Q14" s="2"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="84"/>
-      <c r="B15" s="85"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="85"/>
-      <c r="H15" s="85"/>
+      <c r="A15" s="82"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -21392,12 +21504,6 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="14">
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:H15"/>
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:H13"/>
     <mergeCell ref="B8:H9"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A2:A3"/>
@@ -21406,6 +21512,12 @@
     <mergeCell ref="B4:H5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:H7"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:H15"/>
+    <mergeCell ref="B10:H11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:H13"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -21468,11 +21580,11 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="88"/>
-      <c r="F3" s="89"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="88"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -21586,15 +21698,15 @@
       <c r="R7" s="2"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -23840,18 +23952,18 @@
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -23861,14 +23973,14 @@
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="84"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
+      <c r="A3" s="82"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -23878,18 +23990,18 @@
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -23899,14 +24011,14 @@
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="84"/>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
+      <c r="A5" s="82"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -23916,18 +24028,18 @@
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="82" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -23937,14 +24049,14 @@
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="84"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -23954,18 +24066,18 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="84" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -23975,14 +24087,14 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="84"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
+      <c r="A9" s="82"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -23992,18 +24104,18 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -24013,14 +24125,14 @@
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="84"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -24030,18 +24142,18 @@
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="84" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -24051,14 +24163,14 @@
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -25532,18 +25644,18 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="12">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:H5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:H7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:H9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:H11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:H13"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:H5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -25622,19 +25734,19 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="90" t="s">
+      <c r="D3" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="90" t="s">
+      <c r="J3" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -25796,21 +25908,21 @@
       <c r="Y7" s="2"/>
     </row>
     <row r="8" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="86"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="M8" s="85"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -31974,18 +32086,18 @@
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -31995,14 +32107,14 @@
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="84"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
+      <c r="A3" s="82"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -32012,18 +32124,18 @@
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="83" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -32033,14 +32145,14 @@
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="84"/>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
+      <c r="A5" s="82"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -32050,18 +32162,18 @@
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="82" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -32071,14 +32183,14 @@
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="84"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -32088,18 +32200,18 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -32109,14 +32221,14 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="84"/>
-      <c r="B9" s="85"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
+      <c r="A9" s="82"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -32126,18 +32238,18 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -32147,14 +32259,14 @@
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="84"/>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -32164,18 +32276,18 @@
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -32185,14 +32297,14 @@
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -32202,18 +32314,18 @@
       <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="84" t="s">
+      <c r="A14" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="84" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -32223,14 +32335,14 @@
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="84"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
+      <c r="A15" s="82"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -32240,18 +32352,18 @@
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="84" t="s">
+      <c r="A16" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -32261,14 +32373,14 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="84"/>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="83"/>
+      <c r="A17" s="82"/>
+      <c r="B17" s="84"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -32278,18 +32390,18 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="85" t="s">
+      <c r="B18" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -32299,14 +32411,14 @@
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="84"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
+      <c r="A19" s="82"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -32316,18 +32428,18 @@
       <c r="O19" s="2"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="84" t="s">
+      <c r="A20" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="85" t="s">
+      <c r="B20" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="85"/>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -32337,14 +32449,14 @@
       <c r="O20" s="2"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
-      <c r="B21" s="85"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="85"/>
+      <c r="A21" s="82"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="83"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -32354,18 +32466,18 @@
       <c r="O21" s="2"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="85" t="s">
+      <c r="B22" s="83" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="83"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -32375,14 +32487,14 @@
       <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
-      <c r="B23" s="85"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
+      <c r="A23" s="82"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -33686,12 +33798,11 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="22">
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B20:H21"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B22:H23"/>
-    <mergeCell ref="B18:H19"/>
-    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B8:H9"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="B16:H17"/>
     <mergeCell ref="B14:H15"/>
     <mergeCell ref="B12:H13"/>
@@ -33703,11 +33814,12 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B10:H11"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B8:H9"/>
-    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B20:H21"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B22:H23"/>
+    <mergeCell ref="B18:H19"/>
+    <mergeCell ref="A22:A23"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -33824,40 +33936,40 @@
       <c r="AK2" s="2"/>
     </row>
     <row r="3" spans="1:37" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="89"/>
+      <c r="B3" s="88"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="87" t="s">
+      <c r="E3" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="89"/>
+      <c r="F3" s="88"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="87" t="s">
+      <c r="I3" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="89"/>
+      <c r="J3" s="88"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
-      <c r="M3" s="87" t="s">
+      <c r="M3" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="89"/>
+      <c r="N3" s="88"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
-      <c r="Q3" s="87" t="s">
+      <c r="Q3" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="89"/>
+      <c r="R3" s="88"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-      <c r="U3" s="87" t="s">
+      <c r="U3" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="V3" s="89"/>
+      <c r="V3" s="88"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
@@ -34121,33 +34233,33 @@
       <c r="AK7" s="2"/>
     </row>
     <row r="8" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="86"/>
-      <c r="N8" s="86"/>
-      <c r="O8" s="86"/>
-      <c r="P8" s="86"/>
-      <c r="Q8" s="86"/>
-      <c r="R8" s="86"/>
-      <c r="S8" s="86"/>
-      <c r="T8" s="86"/>
-      <c r="U8" s="86"/>
-      <c r="V8" s="86"/>
-      <c r="W8" s="86"/>
-      <c r="X8" s="86"/>
-      <c r="Y8" s="86"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="M8" s="85"/>
+      <c r="N8" s="85"/>
+      <c r="O8" s="85"/>
+      <c r="P8" s="85"/>
+      <c r="Q8" s="85"/>
+      <c r="R8" s="85"/>
+      <c r="S8" s="85"/>
+      <c r="T8" s="85"/>
+      <c r="U8" s="85"/>
+      <c r="V8" s="85"/>
+      <c r="W8" s="85"/>
+      <c r="X8" s="85"/>
+      <c r="Y8" s="85"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
@@ -40452,18 +40564,18 @@
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -40473,14 +40585,14 @@
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="84"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
+      <c r="A3" s="82"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -40490,18 +40602,18 @@
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="83" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -40511,14 +40623,14 @@
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="84"/>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
+      <c r="A5" s="82"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -40528,18 +40640,18 @@
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="82" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -40549,14 +40661,14 @@
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="84"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -40566,18 +40678,18 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -40587,14 +40699,14 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="84"/>
-      <c r="B9" s="85"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
+      <c r="A9" s="82"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -40604,18 +40716,18 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -40625,14 +40737,14 @@
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="84"/>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -40642,18 +40754,18 @@
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="83" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -40663,14 +40775,14 @@
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
-      <c r="B13" s="85"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="85"/>
-      <c r="H13" s="85"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -40680,18 +40792,18 @@
       <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="84" t="s">
+      <c r="A14" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="84" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -40701,14 +40813,14 @@
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="84"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
+      <c r="A15" s="82"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -40718,18 +40830,18 @@
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="84" t="s">
+      <c r="A16" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="84" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -40739,14 +40851,14 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="84"/>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="83"/>
+      <c r="A17" s="82"/>
+      <c r="B17" s="84"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -40756,18 +40868,18 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="85" t="s">
+      <c r="B18" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -40777,14 +40889,14 @@
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="84"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
+      <c r="A19" s="82"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -40794,14 +40906,14 @@
       <c r="O19" s="2"/>
     </row>
     <row r="20" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="84"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
+      <c r="A20" s="82"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -40811,14 +40923,14 @@
       <c r="O20" s="2"/>
     </row>
     <row r="21" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
-      <c r="B21" s="85"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="85"/>
+      <c r="A21" s="82"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="83"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -40828,14 +40940,14 @@
       <c r="O21" s="2"/>
     </row>
     <row r="22" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
-      <c r="B22" s="85"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
+      <c r="A22" s="82"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="83"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -40845,14 +40957,14 @@
       <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
-      <c r="B23" s="85"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
+      <c r="A23" s="82"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -40863,13 +40975,13 @@
     </row>
     <row r="24" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
-      <c r="B24" s="85"/>
-      <c r="C24" s="85"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="85"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="85"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -40880,13 +40992,13 @@
     </row>
     <row r="25" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="85"/>
-      <c r="C25" s="85"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
+      <c r="B25" s="83"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -42156,6 +42268,18 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="23">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B6:H7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B4:H5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:H9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B12:H13"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B10:H11"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="B20:H21"/>
     <mergeCell ref="B24:H25"/>
@@ -42167,18 +42291,6 @@
     <mergeCell ref="B18:H19"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B14:H15"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:H9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B12:H13"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B4:H5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -42208,57 +42320,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="2" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F1" s="90" t="s">
+      <c r="F1" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
     </row>
     <row r="2" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F2" s="91" t="s">
+      <c r="F2" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="91"/>
+      <c r="G2" s="90"/>
       <c r="H2" s="23">
         <f>D9</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F3" s="91" t="s">
+      <c r="F3" s="90" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="91"/>
+      <c r="G3" s="90"/>
       <c r="H3" s="23">
         <f>I9</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F4" s="91" t="s">
+      <c r="F4" s="90" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="91"/>
+      <c r="G4" s="90"/>
       <c r="H4" s="23">
         <f>N9</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F5" s="91" t="s">
+      <c r="F5" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="91"/>
+      <c r="G5" s="90"/>
       <c r="H5" s="23">
         <f>S9</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F6" s="91" t="s">
+      <c r="F6" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="91"/>
+      <c r="G6" s="90"/>
       <c r="H6" s="37">
         <f>AVERAGE(D9,I9,N9,S9)</f>
         <v>0</v>
